--- a/New_Outputs/ht4_ht6_group_comparison/Stats_HT4_HT6_group_comparison.xlsx
+++ b/New_Outputs/ht4_ht6_group_comparison/Stats_HT4_HT6_group_comparison.xlsx
@@ -814,7 +814,7 @@
         <v>0.1221394125168397</v>
       </c>
       <c r="V2">
-        <v>0.1832091187752596</v>
+        <v>0.1221394125168397</v>
       </c>
       <c r="W2">
         <v>-1.574631891584356</v>
@@ -927,7 +927,7 @@
         <v>0.0271379209252208</v>
       </c>
       <c r="V3">
-        <v>0.08141376277566238</v>
+        <v>0.0271379209252208</v>
       </c>
       <c r="W3">
         <v>2.282008780021758</v>
